--- a/Week 4/Xlookup.xlsx
+++ b/Week 4/Xlookup.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop W11\working_folder\Personales\Upright\Data_Science\Instructor_material\wk4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ab76ec252c957cd7/Desktop/data_bootcamp_folder/instructor_ref/instructor_ref/Week 4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C7888A45-16EE-42AE-9925-25BFA2395575}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="8_{C7888A45-16EE-42AE-9925-25BFA2395575}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F096845D-D550-4253-8192-43D8EA337AB5}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{093018B4-BD74-45BA-99AD-4BE372E656CD}"/>
+    <workbookView xWindow="3490" yWindow="1090" windowWidth="18960" windowHeight="12620" activeTab="2" xr2:uid="{093018B4-BD74-45BA-99AD-4BE372E656CD}"/>
   </bookViews>
   <sheets>
     <sheet name="Background" sheetId="1" r:id="rId1"/>
@@ -426,9 +426,6 @@
     </r>
   </si>
   <si>
-    <t>Carlos Evans</t>
-  </si>
-  <si>
     <t>SN-9942</t>
   </si>
   <si>
@@ -511,6 +508,9 @@
   </si>
   <si>
     <t>Task C: Solving it with XLOOKUP</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -622,7 +622,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -650,19 +650,18 @@
     <xf numFmtId="6" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2402,6 +2401,10 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2722,12 +2725,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99847E35-01CC-4CA3-B422-D7BD48FF328C}">
   <dimension ref="N2:Q9"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="14" max="14" width="16.77734375" customWidth="1"/>
-    <col min="15" max="15" width="18.88671875" customWidth="1"/>
-    <col min="16" max="16" width="21.88671875" customWidth="1"/>
-    <col min="17" max="17" width="20.6640625" customWidth="1"/>
+    <col min="14" max="14" width="16.81640625" customWidth="1"/>
+    <col min="15" max="15" width="18.90625" customWidth="1"/>
+    <col min="16" max="16" width="21.90625" customWidth="1"/>
+    <col min="17" max="17" width="20.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="14:17">
@@ -2749,7 +2752,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="14:17" ht="27.6">
+    <row r="4" spans="14:17" ht="28">
       <c r="N4" s="2" t="s">
         <v>4</v>
       </c>
@@ -2763,7 +2766,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="14:17" ht="27.6">
+    <row r="5" spans="14:17" ht="28">
       <c r="N5" s="2" t="s">
         <v>8</v>
       </c>
@@ -2777,7 +2780,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="14:17" ht="55.2">
+    <row r="6" spans="14:17" ht="56">
       <c r="N6" s="2" t="s">
         <v>11</v>
       </c>
@@ -2791,7 +2794,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="14:17" ht="41.4">
+    <row r="7" spans="14:17" ht="42">
       <c r="N7" s="2" t="s">
         <v>15</v>
       </c>
@@ -2805,7 +2808,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="14:17" ht="55.2">
+    <row r="8" spans="14:17" ht="56">
       <c r="N8" s="2" t="s">
         <v>18</v>
       </c>
@@ -2819,7 +2822,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="14:17" ht="41.4">
+    <row r="9" spans="14:17" ht="42">
       <c r="N9" s="2" t="s">
         <v>22</v>
       </c>
@@ -2842,17 +2845,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{838E53BD-C599-4953-B76F-8E1B3C7A5BCE}">
   <dimension ref="A1:H21"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" customWidth="1"/>
-    <col min="2" max="2" width="20.88671875" customWidth="1"/>
-    <col min="3" max="3" width="11.88671875" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" customWidth="1"/>
+    <col min="2" max="2" width="20.90625" customWidth="1"/>
+    <col min="3" max="3" width="11.90625" customWidth="1"/>
     <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="7" max="7" width="34.5546875" customWidth="1"/>
-    <col min="8" max="8" width="30.21875" customWidth="1"/>
+    <col min="7" max="7" width="34.54296875" customWidth="1"/>
+    <col min="8" max="8" width="30.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="23.4">
+    <row r="1" spans="1:8" ht="23.5">
       <c r="A1" s="7" t="s">
         <v>49</v>
       </c>
@@ -2917,6 +2920,10 @@
       <c r="D7" s="10">
         <v>800</v>
       </c>
+      <c r="H7">
+        <f>VLOOKUP(A11,A6:D9, 4, FALSE)</f>
+        <v>800</v>
+      </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="9" t="s">
@@ -2930,6 +2937,10 @@
       </c>
       <c r="D8" s="10">
         <v>350</v>
+      </c>
+      <c r="H8">
+        <f>VLOOKUP(A11,A6:D9,4)</f>
+        <v>800</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -2990,6 +3001,18 @@
         <v>=INDEX(D6:D9,2)</v>
       </c>
     </row>
+    <row r="14" spans="1:8">
+      <c r="H14">
+        <f>MATCH(A11,A6:A9,0)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="H15" cm="1">
+        <f t="array" ref="H15">INDEX(D6:D9,H14)</f>
+        <v>800</v>
+      </c>
+    </row>
     <row r="16" spans="1:8">
       <c r="G16" s="8" t="s">
         <v>46</v>
@@ -3006,6 +3029,12 @@
       <c r="H17" t="str">
         <f ca="1">+_xlfn.FORMULATEXT(G17)</f>
         <v>=XLOOKUP(A11, A6:A9, D6:D9)</v>
+      </c>
+    </row>
+    <row r="18" spans="6:8">
+      <c r="H18">
+        <f>_xlfn.XLOOKUP(A11,A6:A9,D6:D9)</f>
+        <v>800</v>
       </c>
     </row>
     <row r="20" spans="6:8">
@@ -3026,15 +3055,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DFBF716-6882-46EE-ADD2-64AA7C7F3F2B}">
   <dimension ref="A1:G17"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="15.88671875" customWidth="1"/>
+    <col min="1" max="1" width="15.90625" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="3" width="17.88671875" customWidth="1"/>
-    <col min="6" max="6" width="11.88671875" customWidth="1"/>
+    <col min="3" max="3" width="17.90625" customWidth="1"/>
+    <col min="6" max="6" width="11.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="23.4">
+    <row r="1" spans="1:7" ht="23.5">
       <c r="A1" s="7" t="s">
         <v>50</v>
       </c>
@@ -3046,55 +3075,55 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="C5" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>63</v>
-      </c>
       <c r="F5" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B6" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="C6" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>54</v>
-      </c>
       <c r="F6" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="C7" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="F7" s="15" t="s">
-        <v>67</v>
+      <c r="F7" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B8" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="C8" s="5" t="s">
         <v>59</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>60</v>
       </c>
       <c r="F8" t="str">
         <f>VLOOKUP(A10, A6:D8, 1, TRUE)</f>
@@ -3117,15 +3146,15 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="F12" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -3158,7 +3187,7 @@
     </row>
     <row r="16" spans="1:7">
       <c r="F16" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17" spans="6:7">
